--- a/output/ERRORS.xlsx
+++ b/output/ERRORS.xlsx
@@ -446,23 +446,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>STOCK</t>
+          <t>PRICE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>data\06.04.26 инвентаризация(полн).xlsx</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ValueError</t>
+          <t>MissingInput</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Required REVISION columns not found: НАИМЕНОВАНИЕ / Остаток на складе (шт) на 20.02.2024</t>
+          <t>PRICE file is missing for full pipeline</t>
         </is>
       </c>
     </row>
